--- a/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-14557_Spreadsheet_Steps_Vocabulary_Validation.xlsx
+++ b/DEV/org.openl.rules.test/test-resources/functionality/EPBDS-14557_Spreadsheet_Steps_Vocabulary_Validation.xlsx
@@ -9,9 +9,103 @@
   <sheets>
     <sheet name="Rules" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="30">
+  <si>
+    <t>= new String[] {"NJ","NY"}</t>
+  </si>
+  <si>
+    <t>Check8: Country</t>
+  </si>
+  <si>
+    <t>= new String[] {"CA"}</t>
+  </si>
+  <si>
+    <t>Check9: Country</t>
+  </si>
+  <si>
+    <t>= new String[] {"NY","NJ"}</t>
+  </si>
+  <si>
+    <t>Check10: Country</t>
+  </si>
+  <si>
+    <t>= new String[][] {{"CA"},{"NY","NJ"}}</t>
+  </si>
+  <si>
+    <t>Check11: Country[]</t>
+  </si>
+  <si>
+    <t>= new String[][] {{"US"},{"AB"}}</t>
+  </si>
+  <si>
+    <t>Check12: Country[]</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Check13: Gender</t>
+  </si>
+  <si>
+    <t>Check14: Level</t>
+  </si>
+  <si>
+    <t>Check15: Level</t>
+  </si>
+  <si>
+    <t>= null</t>
+  </si>
+  <si>
+    <t>Check16: Country</t>
+  </si>
+  <si>
+    <t>Check17: Country[]</t>
+  </si>
+  <si>
+    <t>Datatype Country &lt;String&gt;</t>
+  </si>
+  <si>
+    <t>= new String[] {{"CA"},{"NY","NJ"}}</t>
+  </si>
+  <si>
+    <t>= new String[] {{"US"},{"AB"}}</t>
+  </si>
+  <si>
+    <t>= new String[] {"CA","NY","NJ"}</t>
+  </si>
+  <si>
+    <t>= new String[] {"CA", "NY", "NJ"}</t>
+  </si>
+  <si>
+    <t>= new String[] {"CA", "AB"}</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>NJ</t>
+  </si>
+  <si>
+    <t>Check</t>
+  </si>
+  <si>
+    <t>Check10: Country[]</t>
+  </si>
+  <si>
+    <t>= new String[] {"NY", "CA", "NJ")</t>
+  </si>
+  <si>
+    <t>= new String[] {"NY", "CA", "NJ"}</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -21,7 +115,7 @@
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
+      <color theme="1" rgb="000000"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
@@ -44,7 +138,7 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -414,291 +508,232 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:C35"/>
+  <dimension ref="B1:C40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="inlineStr">
+      <c r="B1" t="inlineStr" s="0">
         <is>
           <t>Datatype Gender &lt;String&gt;</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="inlineStr" s="0">
         <is>
           <t>Male</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="inlineStr" s="0">
         <is>
           <t>Female</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
+      <c r="B5" t="inlineStr" s="0">
         <is>
           <t>Datatype Level &lt;Integer&gt;</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="n">
+      <c r="B6" t="n" s="0">
         <v>100</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="n">
+      <c r="B7" t="n" s="0">
         <v>200</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="n">
+      <c r="B8" t="n" s="0">
         <v>300</v>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Datatype Country &lt;String[]&gt;</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>NY, NJ</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-    </row>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
     <row r="14">
-      <c r="B14" t="inlineStr">
+      <c r="B14" t="inlineStr" s="0">
         <is>
           <t>Spreadsheet SpreadsheetResult calls ()</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
+      <c r="B15" t="inlineStr" s="0">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" t="inlineStr" s="0">
         <is>
           <t>Formula</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
+      <c r="B16" t="inlineStr" s="0">
         <is>
           <t>Check1: Gender</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" t="inlineStr" s="0">
         <is>
           <t>Male</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
+      <c r="B17" t="inlineStr" s="0">
         <is>
           <t>Check2: Gender</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" t="inlineStr" s="0">
         <is>
           <t>FMale</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
+      <c r="B18" t="inlineStr" s="0">
         <is>
           <t>Check3: Gender</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" t="inlineStr" s="0">
         <is>
           <t>F3</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
+      <c r="B19" t="inlineStr" s="0">
         <is>
           <t>Check4: Level</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" t="n" s="0">
         <v>100</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
+      <c r="B20" t="inlineStr" s="0">
         <is>
           <t>Check5: Level</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" t="n" s="0">
         <v>999</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
+      <c r="B21" t="inlineStr" s="0">
         <is>
           <t>Check6: Country</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" t="inlineStr" s="0">
         <is>
           <t>AB</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Check7: Country</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>= new String[] {"AB"}</t>
-        </is>
+      <c r="B22" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Check8: Country</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>= new String[] {"NJ","NY"}</t>
-        </is>
+      <c r="B23" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Check9: Country</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>= new String[] {"CA"}</t>
-        </is>
+      <c r="B24" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Check10: Country</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>= new String[] {"NY","NJ"}</t>
-        </is>
+      <c r="B25" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Check11: Country[]</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>= new String[][] {{"CA"},{"NY","NJ"}}</t>
-        </is>
+      <c r="B26" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>200.0</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Check12: Country[]</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>= new String[][] {{"US"},{"AB"}}</t>
-        </is>
+      <c r="B27" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>300.0</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Check13: Gender</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+      <c r="B28" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Check14: Level</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Check15: Level</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Check16: Country</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>= null</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Check17: Country[]</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>= null</t>
-        </is>
-      </c>
-    </row>
+      <c r="B29" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C29" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
     <row r="33"/>
     <row r="34"/>
     <row r="35"/>
+    <row r="37">
+      <c r="B37" t="s" s="0">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
